--- a/examples/baseline.xlsx
+++ b/examples/baseline.xlsx
@@ -70,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -78,6 +78,18 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -87,16 +99,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -112,25 +125,30 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">What it controls</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Provider</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Front Desk</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Nurse</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Biller</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Practice Admin</t>
         </is>
@@ -139,17 +157,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">View patient demographics</t>
+          <t xml:space="preserve">Allow Access to Pt Hub</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Grants or denies users access to the Patient Hub.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -168,6 +186,11 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -176,17 +199,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit patient demographics</t>
+          <t xml:space="preserve">Access Problem List</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Provides access to the Patient's Problem List</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -196,15 +219,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -213,17 +241,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Patient Details</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete patient</t>
+          <t xml:space="preserve">AccountNumber Update</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows the user to modify the patients account number in Patient Demographics.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -242,6 +270,11 @@
         </is>
       </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -250,17 +283,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merge patients</t>
+          <t xml:space="preserve">Allow Access to Patient Merge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows Access to the Patient Merge Functionalities</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -279,6 +312,11 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -287,22 +325,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress Notes</t>
+          <t xml:space="preserve">Administration / System Admin Setup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">View progress notes</t>
+          <t xml:space="preserve">Access to PHI and PII</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Allow or Deny access to the EMR to restrict access to the PHI and PII.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -316,6 +354,11 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -329,17 +372,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock progress notes</t>
+          <t xml:space="preserve">Lock Chart</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Allows the user to lock the chart on a patients Progress Notes.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -353,6 +396,11 @@
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -366,17 +414,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlock progress notes</t>
+          <t xml:space="preserve">Assessment (including Problem List)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Grant access to patient's Assessment (including Problem List) in Progress Notes.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -386,12 +434,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
     </row>
@@ -403,17 +456,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addendum to locked notes</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Access Patient Orders</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -423,10 +476,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -435,27 +493,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Progress Notes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order labs</t>
+          <t xml:space="preserve">Access/View Superbill</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Allows User to Access/View Superbill on Progress Note and all other areas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -465,34 +523,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Orders</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Order imaging</t>
+          <t xml:space="preserve">Edit Addendums</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Allows the original author of the addendum to edit it on a locked progress note.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -501,6 +564,11 @@
         </is>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -509,22 +577,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">Locked Progress Notes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe medications</t>
+          <t xml:space="preserve">Clear My Addendums/Delete Addendums</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Allows the original author to either clear or delete their addendums on a locked note.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -538,6 +606,11 @@
         </is>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -546,22 +619,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prescribe controlled substances (EPCS)</t>
+          <t xml:space="preserve">SS EPrescription</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Allows or denies access to the SureScript ePrescription feature.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -575,6 +648,11 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -583,35 +661,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rx</t>
+          <t xml:space="preserve">SureScripts</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refill medications</t>
+          <t xml:space="preserve">SS Refill Response</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Allow access to the Refill request window from E Jelly Bean -&gt; Refill Request tab.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -625,30 +708,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">View claims</t>
+          <t xml:space="preserve">Batches</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows access to the Batches section in the Billing band.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -662,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit claims</t>
+          <t xml:space="preserve">Close Transactions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows the user to close transactions by time period.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -682,10 +770,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -699,17 +792,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post payments</t>
+          <t xml:space="preserve">Allow users to lock claims</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Grants or denies users permission to lock claims</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -719,10 +812,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -736,12 +834,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write-off / adjustments</t>
+          <t xml:space="preserve">Allow Postings on Locked Insurance Payments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Grants or denies the right to post to a locked insurance payment.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -756,12 +854,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
     </row>
@@ -773,12 +876,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fee schedule</t>
+          <t xml:space="preserve">Accounts LookUp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows access to the Accounts Lookup tool in the Billing band.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -788,7 +891,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -797,6 +900,11 @@
         </is>
       </c>
       <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -805,35 +913,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">View appointments</t>
+          <t xml:space="preserve">Delete Payments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Grants or denies users permission to delete both patient and insurance payments</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -842,27 +955,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book appointments</t>
+          <t xml:space="preserve">Delete Refunds</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Grants or denies user permission to delete refunds.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -871,6 +984,11 @@
         </is>
       </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -879,22 +997,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete appointments</t>
+          <t xml:space="preserve">Changing Fee schedule</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows the user to create a new fee schedule, or update, copy, or delete an existing fee schedule.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -908,6 +1026,11 @@
         </is>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -916,17 +1039,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security settings</t>
+          <t xml:space="preserve">CPT Codes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows the user to create, update, or delete CPT Codes from the Billing menu.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -945,6 +1068,11 @@
         </is>
       </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -953,17 +1081,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Administration / Billing Setup</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">User administration</t>
+          <t xml:space="preserve">Insurances</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows the user to create, update, or delete insurances from the File menu.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -973,7 +1101,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -982,6 +1110,11 @@
         </is>
       </c>
       <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -990,17 +1123,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audit logs</t>
+          <t xml:space="preserve">Allow Access to Block Hours</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows users access to add, update, or delete Appointment Blocks</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1010,7 +1143,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1019,6 +1152,11 @@
         </is>
       </c>
       <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -1027,17 +1165,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Item / CPT / ICD setup</t>
+          <t xml:space="preserve">Allow appointment creation outside working hours</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allow creating appointment out side of working hours.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1047,15 +1185,20 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -1064,22 +1207,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Documents</t>
+          <t xml:space="preserve">Scheduling</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scan / attach documents</t>
+          <t xml:space="preserve">Allow access to Move Appointment to Bump List</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Grants or denies users permission to move appointments to the Bump List.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1093,6 +1236,11 @@
         </is>
       </c>
       <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -1106,12 +1254,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete documents</t>
+          <t xml:space="preserve">Delete Reviewed Document</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows the user to delete a reviewed document in the Patient Documents window.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1130,6 +1278,11 @@
         </is>
       </c>
       <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -1138,17 +1291,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter lab results</t>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Allow user to delete documents from repository</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1158,7 +1311,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1169,43 +1322,53 @@
       <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs</t>
+          <t xml:space="preserve">Documents</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release results to portal</t>
+          <t xml:space="preserve">Bulk Actions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">Allow users to access Bulk Actions on the Review Documents window.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1380,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run financial reports</t>
+          <t xml:space="preserve">Report - Billing Summary</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Allows access to the Billing summary report.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1237,10 +1400,267 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reports</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live Operations Dashboard</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow access to Live Operations Dashboard.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Portal</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Permission to web enable patients</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants or denies users permission to web-enable patients for the Patient Portal.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patient Portal</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Publish/UnPublish Reviewed labs</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants or denies permission to publish reviewed lab results to the Patient Portal.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logs</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security Access Logs</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants or denies users permission to view Security Settings Access logs from the Admin Band.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logs</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access Log Report</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allows the user to view generated access logs.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administration / Users Configuration</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change Password</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The security item provides access to Change Password</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
